--- a/data/trans_orig/IP19-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP19-Clase-trans_orig.xlsx
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57963</t>
+          <t>58485</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74173</t>
+          <t>74614</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58018</t>
+          <t>58127</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73200</t>
+          <t>73292</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121098</t>
+          <t>120779</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>142569</t>
+          <t>142887</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,77%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30179</t>
+          <t>29738</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46389</t>
+          <t>45867</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24345</t>
+          <t>24253</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39527</t>
+          <t>39418</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>59329</t>
+          <t>59011</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>80800</t>
+          <t>81119</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,18%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57505</t>
+          <t>57755</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71104</t>
+          <t>71019</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>53469</t>
+          <t>53352</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>66991</t>
+          <t>66793</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>115546</t>
+          <t>115086</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>134475</t>
+          <t>135287</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>78,04%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16285</t>
+          <t>16370</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29884</t>
+          <t>29634</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18979</t>
+          <t>19177</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32501</t>
+          <t>32618</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38884</t>
+          <t>38072</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57813</t>
+          <t>58273</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,61%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40142</t>
+          <t>40471</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53177</t>
+          <t>53435</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62287</t>
+          <t>61862</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76791</t>
+          <t>77347</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>106569</t>
+          <t>106860</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126147</t>
+          <t>125707</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,4%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14215</t>
+          <t>13957</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27250</t>
+          <t>26921</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22541</t>
+          <t>21985</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37045</t>
+          <t>37470</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>40577</t>
+          <t>41017</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>60155</t>
+          <t>59864</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>123418</t>
+          <t>124499</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>145999</t>
+          <t>146250</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136933</t>
+          <t>136814</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>156983</t>
+          <t>157307</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>268531</t>
+          <t>269315</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>299196</t>
+          <t>297727</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,04%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54044</t>
+          <t>53793</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>76625</t>
+          <t>75544</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>45091</t>
+          <t>44767</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65141</t>
+          <t>65260</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>102921</t>
+          <t>104390</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>133586</t>
+          <t>132802</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,03%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>61436</t>
+          <t>62246</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>76975</t>
+          <t>77462</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>75288</t>
+          <t>75093</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>92332</t>
+          <t>92552</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>142726</t>
+          <t>141818</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>164872</t>
+          <t>165477</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,51%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27145</t>
+          <t>26658</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42684</t>
+          <t>41874</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34957</t>
+          <t>34737</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52001</t>
+          <t>52196</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66538</t>
+          <t>65933</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88684</t>
+          <t>89592</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,72%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>43336</t>
+          <t>43493</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56944</t>
+          <t>56215</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>46461</t>
+          <t>46313</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>58422</t>
+          <t>58436</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>93930</t>
+          <t>94071</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>111406</t>
+          <t>111463</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,69%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17926</t>
+          <t>18655</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>31534</t>
+          <t>31377</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13970</t>
+          <t>13956</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25931</t>
+          <t>26079</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>35856</t>
+          <t>35799</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>53332</t>
+          <t>53191</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,12%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>415445</t>
+          <t>413603</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>454186</t>
+          <t>453303</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>462190</t>
+          <t>461253</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>499287</t>
+          <t>500169</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>889436</t>
+          <t>888505</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>942129</t>
+          <t>939135</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,0%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>183980</t>
+          <t>184863</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>222721</t>
+          <t>224563</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>185316</t>
+          <t>184434</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>222413</t>
+          <t>223350</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>380640</t>
+          <t>383634</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>433333</t>
+          <t>434264</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,83%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48399</t>
+          <t>48252</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63375</t>
+          <t>63398</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57974</t>
+          <t>58332</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71187</t>
+          <t>72032</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111847</t>
+          <t>111499</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131933</t>
+          <t>131608</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,53%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26558</t>
+          <t>26535</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41534</t>
+          <t>41681</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17855</t>
+          <t>17010</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31068</t>
+          <t>30710</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>47042</t>
+          <t>47367</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>67128</t>
+          <t>67476</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,7%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49851</t>
+          <t>50384</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65510</t>
+          <t>65605</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>55592</t>
+          <t>54323</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70115</t>
+          <t>69429</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>109341</t>
+          <t>110196</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>131323</t>
+          <t>131609</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,49%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27756</t>
+          <t>27661</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43415</t>
+          <t>42882</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26022</t>
+          <t>26708</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40545</t>
+          <t>41814</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58080</t>
+          <t>57794</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80062</t>
+          <t>79207</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>41,82%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54712</t>
+          <t>55126</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68376</t>
+          <t>68319</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52198</t>
+          <t>51697</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66209</t>
+          <t>66446</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>109943</t>
+          <t>111175</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130623</t>
+          <t>130239</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,26%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17781</t>
+          <t>17838</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31445</t>
+          <t>31031</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20681</t>
+          <t>20444</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34692</t>
+          <t>35193</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42424</t>
+          <t>42808</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63104</t>
+          <t>61872</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>139930</t>
+          <t>138295</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>160372</t>
+          <t>159744</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>168706</t>
+          <t>168329</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>187524</t>
+          <t>187908</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>313477</t>
+          <t>314468</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>341681</t>
+          <t>344250</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,57%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45736</t>
+          <t>46364</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>66178</t>
+          <t>67813</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39025</t>
+          <t>38641</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57843</t>
+          <t>58220</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>90976</t>
+          <t>88407</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>119180</t>
+          <t>118189</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>97570</t>
+          <t>96838</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>115907</t>
+          <t>115221</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>83797</t>
+          <t>82651</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>101275</t>
+          <t>101281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>186933</t>
+          <t>186819</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>212479</t>
+          <t>212990</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,5%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33262</t>
+          <t>33948</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51599</t>
+          <t>52331</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39339</t>
+          <t>39333</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56817</t>
+          <t>57963</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>77304</t>
+          <t>76793</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>102850</t>
+          <t>102964</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,53%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32184</t>
+          <t>32584</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43131</t>
+          <t>43185</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>42028</t>
+          <t>43143</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>56221</t>
+          <t>56620</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>79943</t>
+          <t>78526</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>96588</t>
+          <t>96449</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,82%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10780</t>
+          <t>10726</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21727</t>
+          <t>21327</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>16674</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>31266</t>
+          <t>30151</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30617</t>
+          <t>30756</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>47262</t>
+          <t>48679</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>38,27%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>451248</t>
+          <t>450189</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>491803</t>
+          <t>490621</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>486726</t>
+          <t>491093</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>527521</t>
+          <t>531845</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>953039</t>
+          <t>953759</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1010239</t>
+          <t>1010034</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,61%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>186741</t>
+          <t>187923</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>227296</t>
+          <t>228355</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>185005</t>
+          <t>180681</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>225800</t>
+          <t>221433</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>380831</t>
+          <t>381036</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>438031</t>
+          <t>437311</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,44%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47810</t>
+          <t>47189</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62020</t>
+          <t>61440</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64952</t>
+          <t>64435</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79388</t>
+          <t>79778</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115658</t>
+          <t>116320</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>136969</t>
+          <t>136706</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,75%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21070</t>
+          <t>21650</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35280</t>
+          <t>35901</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20409</t>
+          <t>20019</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34845</t>
+          <t>35362</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>45918</t>
+          <t>46181</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>67229</t>
+          <t>66567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,4%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62796</t>
+          <t>61999</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78609</t>
+          <t>78210</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>64523</t>
+          <t>65338</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81426</t>
+          <t>81520</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>131731</t>
+          <t>132669</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>154702</t>
+          <t>155846</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>71,34%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27105</t>
+          <t>27504</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42918</t>
+          <t>43715</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31320</t>
+          <t>31226</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48223</t>
+          <t>47408</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63758</t>
+          <t>62614</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86729</t>
+          <t>85791</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,27%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32918</t>
+          <t>33401</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44897</t>
+          <t>45220</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48303</t>
+          <t>48557</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61660</t>
+          <t>60994</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85211</t>
+          <t>84070</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103100</t>
+          <t>103062</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,08%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>16620</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28922</t>
+          <t>28439</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13768</t>
+          <t>14434</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27125</t>
+          <t>26871</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34168</t>
+          <t>34206</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52057</t>
+          <t>53198</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,75%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>148149</t>
+          <t>149471</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>171296</t>
+          <t>170636</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>145318</t>
+          <t>145051</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>165568</t>
+          <t>166105</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>301443</t>
+          <t>300663</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>331063</t>
+          <t>329509</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>75,85%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52281</t>
+          <t>52941</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>75428</t>
+          <t>74106</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>45286</t>
+          <t>44749</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65536</t>
+          <t>65803</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>103368</t>
+          <t>104922</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>132988</t>
+          <t>133768</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,79%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>90255</t>
+          <t>90680</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>107354</t>
+          <t>107420</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>98778</t>
+          <t>98832</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>115717</t>
+          <t>115758</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>194664</t>
+          <t>193898</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>217624</t>
+          <t>219460</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>78,58%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28840</t>
+          <t>28774</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45939</t>
+          <t>45514</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27371</t>
+          <t>27330</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44310</t>
+          <t>44256</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>61658</t>
+          <t>59822</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84618</t>
+          <t>85384</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,57%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>35745</t>
+          <t>35072</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47089</t>
+          <t>47092</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40819</t>
+          <t>41579</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>53427</t>
+          <t>53703</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>80441</t>
+          <t>80307</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>97720</t>
+          <t>97444</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,59%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13998</t>
+          <t>13995</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25342</t>
+          <t>26015</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14398</t>
+          <t>14122</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27006</t>
+          <t>26246</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>31192</t>
+          <t>31468</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>48471</t>
+          <t>48605</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,7%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>444533</t>
+          <t>448081</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>483911</t>
+          <t>486500</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>491705</t>
+          <t>491261</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>533380</t>
+          <t>531811</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>951315</t>
+          <t>952852</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1006124</t>
+          <t>1005496</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,8%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>187591</t>
+          <t>185002</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>226969</t>
+          <t>223421</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>176357</t>
+          <t>177926</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>218032</t>
+          <t>218476</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>375115</t>
+          <t>375743</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>429924</t>
+          <t>428387</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,01%</t>
         </is>
       </c>
     </row>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21823</t>
+          <t>22086</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36612</t>
+          <t>37294</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26353</t>
+          <t>27074</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51096</t>
+          <t>51367</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54455</t>
+          <t>53695</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84273</t>
+          <t>81137</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28089</t>
+          <t>27603</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45810</t>
+          <t>46104</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36724</t>
+          <t>37658</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59677</t>
+          <t>59015</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69164</t>
+          <t>69183</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99427</t>
+          <t>97773</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>41,5%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30090</t>
+          <t>29595</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46992</t>
+          <t>46581</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37556</t>
+          <t>36932</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58845</t>
+          <t>59989</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>71694</t>
+          <t>72964</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>99624</t>
+          <t>99662</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21982</t>
+          <t>22645</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36483</t>
+          <t>37061</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>15418</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28763</t>
+          <t>28609</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>41444</t>
+          <t>41199</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61087</t>
+          <t>60864</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,99%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23792</t>
+          <t>23915</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38506</t>
+          <t>38795</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29925</t>
+          <t>30276</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47718</t>
+          <t>47217</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>57565</t>
+          <t>59126</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>80270</t>
+          <t>81116</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,64%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27328</t>
+          <t>27008</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42127</t>
+          <t>42340</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>27034</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44599</t>
+          <t>43340</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60205</t>
+          <t>59361</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81746</t>
+          <t>81940</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,07%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13986</t>
+          <t>14395</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26074</t>
+          <t>26175</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16217</t>
+          <t>16839</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30498</t>
+          <t>30282</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>34653</t>
+          <t>34231</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>53373</t>
+          <t>52199</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>45,67%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11137</t>
+          <t>10856</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22725</t>
+          <t>22363</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16136</t>
+          <t>16175</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30382</t>
+          <t>30208</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30718</t>
+          <t>29622</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48917</t>
+          <t>48859</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,74%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9867</t>
+          <t>10233</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20016</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11579</t>
+          <t>11468</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24500</t>
+          <t>24652</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23955</t>
+          <t>23987</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40921</t>
+          <t>41730</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43235</t>
+          <t>45254</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86517</t>
+          <t>87691</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61324</t>
+          <t>60244</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>86432</t>
+          <t>86796</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113282</t>
+          <t>113792</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>162299</t>
+          <t>162714</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,84%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>65566</t>
+          <t>64540</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134994</t>
+          <t>135822</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61547</t>
+          <t>61523</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91391</t>
+          <t>90848</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>138433</t>
+          <t>139441</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>220251</t>
+          <t>222191</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,67%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34746</t>
+          <t>36500</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70084</t>
+          <t>69630</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55151</t>
+          <t>54648</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82703</t>
+          <t>84303</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>96851</t>
+          <t>96498</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>145407</t>
+          <t>145155</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,75%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34402</t>
+          <t>35177</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52412</t>
+          <t>52075</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38932</t>
+          <t>38129</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63744</t>
+          <t>62794</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>78719</t>
+          <t>79957</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>108923</t>
+          <t>109582</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,66%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36711</t>
+          <t>36951</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>56102</t>
+          <t>56951</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46395</t>
+          <t>45678</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>74508</t>
+          <t>73258</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>89694</t>
+          <t>90001</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>123662</t>
+          <t>123350</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,64%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19570</t>
+          <t>19209</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>35645</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33491</t>
+          <t>35008</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71035</t>
+          <t>74235</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59240</t>
+          <t>57789</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>103308</t>
+          <t>99830</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>36,13%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15761</t>
+          <t>15866</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28681</t>
+          <t>28860</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16217</t>
+          <t>16907</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29892</t>
+          <t>31054</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>35890</t>
+          <t>35495</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>54253</t>
+          <t>54596</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>39,22%</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21683</t>
+          <t>21375</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35733</t>
+          <t>35856</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22930</t>
+          <t>23866</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>38349</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>49485</t>
+          <t>49536</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>69602</t>
+          <t>71005</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>51,0%</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11978</t>
+          <t>11959</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25440</t>
+          <t>25714</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>10665</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24902</t>
+          <t>23841</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>25724</t>
+          <t>25284</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>45220</t>
+          <t>44593</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,03%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>183987</t>
+          <t>175482</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>238121</t>
+          <t>236148</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>203910</t>
+          <t>206632</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>253630</t>
+          <t>255686</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>405071</t>
+          <t>403631</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>477730</t>
+          <t>474360</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>219380</t>
+          <t>217948</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>304087</t>
+          <t>308792</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>252953</t>
+          <t>250728</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>307413</t>
+          <t>302929</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>487320</t>
+          <t>481701</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>584341</t>
+          <t>579681</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>41,83%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>162400</t>
+          <t>161888</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>210180</t>
+          <t>211572</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>207701</t>
+          <t>209093</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>266842</t>
+          <t>264362</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>384714</t>
+          <t>385142</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>459062</t>
+          <t>463348</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
